--- a/公司清單.xlsx
+++ b/公司清單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niuji\Documents\mops_pdf_packager-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17830B3-A102-4A3A-82CE-B02DFAB6DD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BEA35D-B765-4F00-93B7-F526B7B4F65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>股票代碼</t>
   </si>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -459,7 +459,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2330</v>
+        <v>1730</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -467,26 +467,9 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2317</v>
-      </c>
-      <c r="B3">
-        <v>110</v>
-      </c>
-      <c r="C3">
-        <v>115</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3008</v>
-      </c>
-      <c r="I4" t="s">
+        <v>3577</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>

--- a/公司清單.xlsx
+++ b/公司清單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niuji\Documents\mops_pdf_packager-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BEA35D-B765-4F00-93B7-F526B7B4F65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9D239B-8D68-4908-A987-7552B4AFCAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>股票代碼</t>
   </si>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -473,6 +473,20 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2330</v>
+      </c>
+      <c r="B4">
+        <v>112</v>
+      </c>
+      <c r="C4">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
